--- a/exports/TATAELXSI_full_report.xlsx
+++ b/exports/TATAELXSI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.25</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>7265</v>
+        <v>6972</v>
       </c>
       <c r="I2" t="n">
         <v>7001.073569370797</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>21.41</v>
+        <v>16.52</v>
       </c>
       <c r="L2" t="n">
         <v>2.9</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.02</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44623.55208333334</v>
+        <v>44624.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>6680</v>
+        <v>6750</v>
       </c>
       <c r="I3" t="n">
         <v>6720.211134415507</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K3" t="n">
-        <v>4.19</v>
+        <v>3.18</v>
       </c>
       <c r="L3" t="n">
         <v>14.17</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>8372.6</v>
+        <v>7912.85</v>
       </c>
       <c r="I4" t="n">
         <v>8207.292754842518</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K4" t="n">
-        <v>24.04</v>
+        <v>17.23</v>
       </c>
       <c r="L4" t="n">
         <v>4.22</v>
@@ -669,7 +716,7 @@
         <v>1.36</v>
       </c>
       <c r="N4" t="n">
-        <v>5.51</v>
+        <v>6.54</v>
       </c>
       <c r="O4" t="n">
         <v>-0.27</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>11.41</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44693.55208333334</v>
+        <v>44694.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>6893.95</v>
+        <v>7826.7</v>
       </c>
       <c r="I5" t="n">
         <v>7488.031323357079</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K5" t="n">
-        <v>12.88</v>
+        <v>1.09</v>
       </c>
       <c r="L5" t="n">
         <v>7.12</v>
       </c>
       <c r="M5" t="n">
-        <v>2.34</v>
+        <v>4.15</v>
       </c>
       <c r="N5" t="n">
-        <v>6.32</v>
+        <v>14.3</v>
       </c>
       <c r="O5" t="n">
         <v>-6.54</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>17.55</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>8160</v>
+        <v>7833.8</v>
       </c>
       <c r="I6" t="n">
         <v>8093.535261877936</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>4.26</v>
+        <v>0.09</v>
       </c>
       <c r="L6" t="n">
         <v>8.470000000000001</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.74</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44740.55208333334</v>
+        <v>44741.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>8051</v>
+        <v>8152</v>
       </c>
       <c r="I7" t="n">
         <v>8087.82951928235</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.77</v>
+        <v>-4.06</v>
       </c>
       <c r="L7" t="n">
         <v>6.83</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44755.38541666666</v>
+        <v>44755.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>7797.2</v>
+        <v>7716</v>
       </c>
       <c r="I8" t="n">
         <v>7720.396724926495</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.35</v>
+        <v>-5.35</v>
       </c>
       <c r="L8" t="n">
-        <v>4.54</v>
+        <v>5.73</v>
       </c>
       <c r="M8" t="n">
         <v>0.63</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44763.38541666666</v>
+        <v>44763.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>8130</v>
+        <v>8225</v>
       </c>
       <c r="I9" t="n">
         <v>8177.777902659741</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.37</v>
+        <v>-6.6</v>
       </c>
       <c r="L9" t="n">
-        <v>6.46</v>
+        <v>6.69</v>
       </c>
       <c r="M9" t="n">
         <v>1.64</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>5.35</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>10120.3</v>
+        <v>9771.049999999999</v>
       </c>
       <c r="I10" t="n">
         <v>9996.854066961094</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>23.04</v>
+        <v>18.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="N10" t="n">
         <v>4.57</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44894.55208333334</v>
+        <v>44895.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>6785</v>
+        <v>6955.1</v>
       </c>
       <c r="I11" t="n">
         <v>6874.383099738314</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>99.16666666666667</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>30.56</v>
+        <v>28.82</v>
       </c>
       <c r="L11" t="n">
         <v>3.36</v>
@@ -1068,7 +1199,7 @@
         <v>2.39</v>
       </c>
       <c r="N11" t="n">
-        <v>2.34</v>
+        <v>3.11</v>
       </c>
       <c r="O11" t="n">
         <v>-3.39</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.83</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44903.38541666666</v>
+        <v>44903.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>6846.55</v>
+        <v>6825</v>
       </c>
       <c r="I12" t="n">
         <v>6838.733236227321</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.56</v>
+        <v>-1.87</v>
       </c>
       <c r="L12" t="n">
         <v>2.5</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>3.3</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44918.55208333334</v>
+        <v>44921.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>5844</v>
+        <v>6173.05</v>
       </c>
       <c r="I13" t="n">
         <v>6121.483851890266</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>14.37</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>0.64</v>
@@ -1182,7 +1337,7 @@
         <v>0.84</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.63</v>
       </c>
       <c r="O13" t="n">
         <v>-0.25</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.85</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44979.55208333334</v>
+        <v>44980.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>6518</v>
+        <v>6473.65</v>
       </c>
       <c r="I14" t="n">
         <v>6475.704184520027</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K14" t="n">
-        <v>5.59</v>
+        <v>4.87</v>
       </c>
       <c r="L14" t="n">
         <v>7.46</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>3.7</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45022.55208333334</v>
+        <v>45026.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>6080</v>
+        <v>6165.25</v>
       </c>
       <c r="I15" t="n">
         <v>6161.056079290673</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K15" t="n">
-        <v>6.08</v>
+        <v>4.76</v>
       </c>
       <c r="L15" t="n">
         <v>0.79</v>
@@ -1296,7 +1475,7 @@
         <v>1.81</v>
       </c>
       <c r="N15" t="n">
-        <v>1.64</v>
+        <v>2.53</v>
       </c>
       <c r="O15" t="n">
         <v>-0.43</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.2</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>7675</v>
+        <v>7565</v>
       </c>
       <c r="I16" t="n">
         <v>7577.97577181509</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K16" t="n">
-        <v>24.49</v>
+        <v>22.7</v>
       </c>
       <c r="L16" t="n">
         <v>1.95</v>
@@ -1353,7 +1544,7 @@
         <v>1.29</v>
       </c>
       <c r="N16" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="O16" t="n">
         <v>2.53</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.39</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45120.55208333334</v>
+        <v>45121.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>7572</v>
+        <v>7679.9</v>
       </c>
       <c r="I17" t="n">
         <v>7634.099611300976</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09</v>
+        <v>-1.52</v>
       </c>
       <c r="L17" t="n">
         <v>1.6</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.4</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45127.38541666666</v>
+        <v>45127.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>7530</v>
+        <v>7490</v>
       </c>
       <c r="I18" t="n">
         <v>7500.217658923684</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.95</v>
+        <v>-2.47</v>
       </c>
       <c r="L18" t="n">
         <v>4.36</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>4.17</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45161.55208333334</v>
+        <v>45162.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>7120</v>
+        <v>7278.9</v>
       </c>
       <c r="I19" t="n">
         <v>7197.056286678154</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>4.94</v>
+        <v>2.82</v>
       </c>
       <c r="L19" t="n">
         <v>0.63</v>
       </c>
       <c r="M19" t="n">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37</v>
+        <v>2.36</v>
       </c>
       <c r="O19" t="n">
         <v>-0.78</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.61</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>7475.25</v>
+        <v>7360</v>
       </c>
       <c r="I20" t="n">
         <v>7436.336402530786</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>1.11</v>
       </c>
       <c r="L20" t="n">
         <v>3.1</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.19</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>7613.5</v>
+        <v>7802.8</v>
       </c>
       <c r="I21" t="n">
         <v>7742.093186299551</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.44</v>
+        <v>-6.02</v>
       </c>
       <c r="L21" t="n">
-        <v>4.42</v>
+        <v>6.48</v>
       </c>
       <c r="M21" t="n">
         <v>0.96</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="O21" t="n">
         <v>-2.24</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.3</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>8870.25</v>
+        <v>8589</v>
       </c>
       <c r="I22" t="n">
         <v>8632.585013059586</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>13.68</v>
+        <v>10.08</v>
       </c>
       <c r="L22" t="n">
         <v>1.83</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.33</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45342.38541666666</v>
+        <v>45342.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>7635.65</v>
+        <v>7769.85</v>
       </c>
       <c r="I23" t="n">
         <v>7732.915504406446</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>61.83333333333334</v>
+        <v>62</v>
       </c>
       <c r="K23" t="n">
-        <v>11.1</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>4.19</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.21</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>7649</v>
+        <v>7565</v>
       </c>
       <c r="I24" t="n">
         <v>7580.723809140247</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.56</v>
+        <v>-2.64</v>
       </c>
       <c r="L24" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="M24" t="n">
         <v>-0</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>5.42</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45351.38541666666</v>
+        <v>45351.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>7539.7</v>
+        <v>7916.4</v>
       </c>
       <c r="I25" t="n">
         <v>7850.464468898825</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>0.33</v>
+        <v>-4.65</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>5.09</v>
       </c>
       <c r="M25" t="n">
         <v>0.6</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.52</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>7597.05</v>
+        <v>7399</v>
       </c>
       <c r="I26" t="n">
         <v>7469.597530191952</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.03</v>
+        <v>-6.54</v>
       </c>
       <c r="L26" t="n">
-        <v>5.07</v>
+        <v>7.34</v>
       </c>
       <c r="M26" t="n">
         <v>0.64</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>8.07</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>7705</v>
+        <v>8036.25</v>
       </c>
       <c r="I27" t="n">
         <v>7988.261047517596</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.14</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>6.37</v>
+        <v>9.56</v>
       </c>
       <c r="M27" t="n">
         <v>1.18</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>7.09</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>7755</v>
+        <v>7593</v>
       </c>
       <c r="I28" t="n">
         <v>7699.338696291207</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.5</v>
+        <v>-5.52</v>
       </c>
       <c r="L28" t="n">
-        <v>4.61</v>
+        <v>5.73</v>
       </c>
       <c r="M28" t="n">
-        <v>0.03</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.61</v>
+        <v>2.44</v>
       </c>
       <c r="O28" t="n">
         <v>3.98</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.66</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>7294</v>
+        <v>7338.1</v>
       </c>
       <c r="I29" t="n">
         <v>7320.896954108224</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K29" t="n">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="L29" t="n">
         <v>1.54</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>3.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>7210.55</v>
+        <v>7116.2</v>
       </c>
       <c r="I30" t="n">
         <v>7120.605735078722</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.74</v>
+        <v>-3.02</v>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>3.24</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
         <v>0.82</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>4.65</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45455.55208333334</v>
+        <v>45456.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>7143</v>
+        <v>7231.9</v>
       </c>
       <c r="I31" t="n">
         <v>7163.306586367903</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.38</v>
+        <v>-1.63</v>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="M31" t="n">
         <v>3.21</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>4.69</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45469.55208333334</v>
+        <v>45470.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>7090</v>
+        <v>6983</v>
       </c>
       <c r="I32" t="n">
         <v>7013.016616543759</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.96</v>
+        <v>-3.44</v>
       </c>
       <c r="L32" t="n">
-        <v>2.17</v>
+        <v>3.47</v>
       </c>
       <c r="M32" t="n">
         <v>0.83</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45526.55208333334</v>
+        <v>45527.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>6949.5</v>
+        <v>6980</v>
       </c>
       <c r="I33" t="n">
         <v>6978.007183420877</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K33" t="n">
-        <v>0.48</v>
+        <v>0.04</v>
       </c>
       <c r="L33" t="n">
         <v>2.75</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>3.61</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45532.55208333334</v>
+        <v>45533.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>8180</v>
+        <v>7970.6</v>
       </c>
       <c r="I34" t="n">
         <v>8059.456994051033</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>17.19</v>
+        <v>14.19</v>
       </c>
       <c r="L34" t="n">
         <v>0.71</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.33</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45555.38541666666</v>
+        <v>45555.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>7715.45</v>
+        <v>7900</v>
       </c>
       <c r="I35" t="n">
         <v>7870.601823028972</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>3.2</v>
+        <v>0.89</v>
       </c>
       <c r="L35" t="n">
         <v>4.7</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>6.75</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>7599</v>
+        <v>7543.9</v>
       </c>
       <c r="I36" t="n">
         <v>7549.898695751643</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.81</v>
+        <v>-4.51</v>
       </c>
       <c r="L36" t="n">
-        <v>4.18</v>
+        <v>5.68</v>
       </c>
       <c r="M36" t="n">
         <v>1.04</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.32</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45628.55208333334</v>
+        <v>45629.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>6702</v>
+        <v>7129</v>
       </c>
       <c r="I37" t="n">
         <v>6853.999868827565</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K37" t="n">
-        <v>11.16</v>
+        <v>5.5</v>
       </c>
       <c r="L37" t="n">
         <v>6.4</v>
@@ -2550,7 +2993,7 @@
         <v>1.72</v>
       </c>
       <c r="N37" t="n">
-        <v>3.68</v>
+        <v>5.79</v>
       </c>
       <c r="O37" t="n">
         <v>-0.51</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.59</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>7235.1</v>
+        <v>7015.05</v>
       </c>
       <c r="I38" t="n">
         <v>7077.722822819406</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>1.49</v>
+        <v>-1.6</v>
       </c>
       <c r="L38" t="n">
         <v>5.46</v>
@@ -2607,7 +3062,7 @@
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>0.85</v>
+        <v>4.28</v>
       </c>
       <c r="O38" t="n">
         <v>5.79</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.44</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>5370</v>
+        <v>5478</v>
       </c>
       <c r="I39" t="n">
         <v>5446.313520101282</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>90.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K39" t="n">
-        <v>23.45</v>
+        <v>21.91</v>
       </c>
       <c r="L39" t="n">
         <v>4.42</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.52</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45743.55208333334</v>
+        <v>45744.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>5415.05</v>
+        <v>5250</v>
       </c>
       <c r="I40" t="n">
         <v>5324.11275456816</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.15</v>
+        <v>-4.16</v>
       </c>
       <c r="L40" t="n">
-        <v>2.85</v>
+        <v>4.51</v>
       </c>
       <c r="M40" t="n">
         <v>1.13</v>
       </c>
       <c r="N40" t="n">
-        <v>2.65</v>
+        <v>3.97</v>
       </c>
       <c r="O40" t="n">
         <v>1.77</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>4895</v>
+        <v>5365.5</v>
       </c>
       <c r="I41" t="n">
         <v>5143.030093270083</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>6.76</v>
+        <v>-2.2</v>
       </c>
       <c r="L41" t="n">
         <v>3.56</v>
@@ -2778,7 +3269,7 @@
         <v>2.36</v>
       </c>
       <c r="N41" t="n">
-        <v>3.72</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="O41" t="n">
         <v>-3.97</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.17</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>6554</v>
+        <v>6450</v>
       </c>
       <c r="I42" t="n">
         <v>6462.055794307841</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>22.15</v>
+        <v>20.21</v>
       </c>
       <c r="L42" t="n">
         <v>10.45</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.66</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45852.55208333334</v>
+        <v>45853.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>6178.5</v>
+        <v>6393.5</v>
       </c>
       <c r="I43" t="n">
         <v>6186.720399755029</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>32</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K43" t="n">
-        <v>4.21</v>
+        <v>0.88</v>
       </c>
       <c r="L43" t="n">
         <v>1.62</v>
@@ -2892,7 +3407,7 @@
         <v>1.34</v>
       </c>
       <c r="N43" t="n">
-        <v>2.29</v>
+        <v>3.26</v>
       </c>
       <c r="O43" t="n">
         <v>-2.54</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.87</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45873.55208333334</v>
+        <v>45874.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>6027</v>
+        <v>5987.5</v>
       </c>
       <c r="I44" t="n">
         <v>5998.496355898576</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.73</v>
+        <v>-6.35</v>
       </c>
       <c r="L44" t="n">
         <v>6.58</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>4.38</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>5472.5</v>
+        <v>5480.5</v>
       </c>
       <c r="I45" t="n">
         <v>5477.496771363415</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K45" t="n">
-        <v>8.6</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L45" t="n">
         <v>1.13</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.44</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>5606</v>
+        <v>5510.5</v>
       </c>
       <c r="I46" t="n">
         <v>5525.078751338405</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>2.29</v>
+        <v>0.55</v>
       </c>
       <c r="L46" t="n">
         <v>0.58</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.65</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45938.55208333334</v>
+        <v>45939.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>5450</v>
+        <v>5514</v>
       </c>
       <c r="I47" t="n">
         <v>5450.476685627944</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K47" t="n">
-        <v>1.1</v>
+        <v>-0.06</v>
       </c>
       <c r="L47" t="n">
         <v>2.35</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.34</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>5375</v>
+        <v>5255</v>
       </c>
       <c r="I48" t="n">
         <v>5358.853839840292</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.52</v>
+        <v>-4.7</v>
       </c>
       <c r="L48" t="n">
-        <v>4.43</v>
+        <v>5.3</v>
       </c>
       <c r="M48" t="n">
         <v>0.58</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.17</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>5296</v>
+        <v>5438</v>
       </c>
       <c r="I49" t="n">
         <v>5392.73389670244</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.78</v>
+        <v>-3.48</v>
       </c>
       <c r="L49" t="n">
-        <v>2.37</v>
+        <v>4.28</v>
       </c>
       <c r="M49" t="n">
         <v>0.14</v>
       </c>
       <c r="N49" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="O49" t="n">
         <v>-2.74</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.91</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45989.38541666666</v>
+        <v>45989.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>5163.5</v>
+        <v>5156</v>
       </c>
       <c r="I50" t="n">
         <v>5159.550204202559</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.05</v>
+        <v>-5.19</v>
       </c>
       <c r="L50" t="n">
         <v>5.76</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>4.03</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5046</v>
+        <v>5353.5</v>
       </c>
       <c r="I51" t="n">
         <v>5099.682383274432</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>2.13</v>
+        <v>-3.83</v>
       </c>
       <c r="L51" t="n">
-        <v>2.19</v>
+        <v>4.1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.7</v>
+        <v>1.39</v>
       </c>
       <c r="N51" t="n">
-        <v>3.13</v>
+        <v>7.21</v>
       </c>
       <c r="O51" t="n">
         <v>-0.66</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.86</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46036.38541666666</v>
+        <v>46036.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>5550</v>
+        <v>5475</v>
       </c>
       <c r="I52" t="n">
         <v>5482.354083811122</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>3.67</v>
+        <v>2.27</v>
       </c>
       <c r="L52" t="n">
         <v>5.45</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.07</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46118.55208333334</v>
+        <v>46119.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>4287</v>
+        <v>4353.1</v>
       </c>
       <c r="I53" t="n">
         <v>4313.520754070011</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>82</v>
+        <v>82.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>21.7</v>
+        <v>20.49</v>
       </c>
       <c r="L53" t="n">
         <v>3.98</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46134.38541666666</v>
+        <v>46134.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>4417.7</v>
+        <v>4352</v>
       </c>
       <c r="I54" t="n">
         <v>4374.470861936484</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>1.48</v>
+        <v>-0.03</v>
       </c>
       <c r="L54" t="n">
         <v>3.38</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.06</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46163.38541666666</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>4197.6</v>
+        <v>4218</v>
       </c>
       <c r="I55" t="n">
         <v>4210.128240547517</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K55" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="L55" t="n">
         <v>1.56</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.7</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>4285</v>
+        <v>4239.3</v>
       </c>
       <c r="I56" t="n">
         <v>4276.999914914491</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K56" t="n">
-        <v>1.59</v>
+        <v>0.5</v>
       </c>
       <c r="L56" t="n">
         <v>0.96</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.02</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>3700</v>
+        <v>3811.2</v>
       </c>
       <c r="I57" t="n">
         <v>3799.597606380721</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>32</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>12.72</v>
+        <v>10.1</v>
       </c>
       <c r="L57" t="n">
         <v>1.25</v>
@@ -3690,7 +4373,7 @@
         <v>1.64</v>
       </c>
       <c r="N57" t="n">
-        <v>2.18</v>
+        <v>3.65</v>
       </c>
       <c r="O57" t="n">
         <v>-1.25</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.02</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46217.55208333334</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>3710</v>
+        <v>3486.7</v>
       </c>
       <c r="I58" t="n">
         <v>3611.562220453609</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.66</v>
+        <v>-8.51</v>
       </c>
       <c r="L58" t="n">
-        <v>3.63</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3</v>
+        <v>4.77</v>
       </c>
       <c r="N58" t="n">
-        <v>3.26</v>
+        <v>4.72</v>
       </c>
       <c r="O58" t="n">
         <v>3.65</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46230.55208333334</v>
+        <v>46231.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>3555</v>
+        <v>3587.5</v>
       </c>
       <c r="I59" t="n">
         <v>3557.201172556853</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.96</v>
+        <v>-2.89</v>
       </c>
       <c r="L59" t="n">
-        <v>3.08</v>
+        <v>4.11</v>
       </c>
       <c r="M59" t="n">
         <v>0.53</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.03</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46258.55208333334</v>
+        <v>46259.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>3685</v>
+        <v>3617.8</v>
       </c>
       <c r="I60" t="n">
         <v>3645.193557233392</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K60" t="n">
-        <v>2.72</v>
+        <v>0.84</v>
       </c>
       <c r="L60" t="n">
         <v>0.75</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.99</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46304.55208333334</v>
+        <v>46307.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>3144.8</v>
+        <v>3281.2</v>
       </c>
       <c r="I61" t="n">
         <v>3183.11809536127</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K61" t="n">
-        <v>13.07</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L61" t="n">
         <v>2.49</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3978,6 +4721,14 @@
       <c r="Q62" t="n">
         <v>24</v>
       </c>
+      <c r="R62" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6080,7 +6831,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.8</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="6">
@@ -6090,7 +6841,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6100,7 +6851,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -6110,7 +6861,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6120,7 +6871,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="10">
@@ -6130,7 +6881,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -6140,7 +6891,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -6150,7 +6901,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6160,7 +6911,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="14">
@@ -6170,7 +6921,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -6180,7 +6931,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.34</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="16">
@@ -6190,7 +6941,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.05</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="17">
@@ -6200,7 +6951,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.56</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="18">
@@ -6210,7 +6961,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.3</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="19">
@@ -6220,7 +6971,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.67</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="20">
@@ -6230,7 +6981,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.09</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="21">
@@ -6250,7 +7001,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -6270,7 +7021,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="25">
@@ -6280,7 +7031,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.55</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="26">
@@ -6290,7 +7041,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.17</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +7051,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.6</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="28">
@@ -6310,7 +7061,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
